--- a/XLSX/Player.xlsx
+++ b/XLSX/Player.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\dodge-ball-raylib\XLSX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\dodge-ball\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DFAE46-F2DE-4EC2-BF97-729E8B347D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1AA0EC-206B-4CB7-83B0-798B78015EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="+Player" sheetId="1" r:id="rId1"/>
@@ -402,6 +402,7 @@
   <cols>
     <col min="1" max="1" width="23.59765625" customWidth="1"/>
     <col min="2" max="2" width="25.19921875" customWidth="1"/>
+    <col min="3" max="3" width="22.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
